--- a/examples/macro/macro.xlsx
+++ b/examples/macro/macro.xlsx
@@ -25,7 +25,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,11 +38,6 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="00444444"/>
-      <sz val="8"/>
-    </font>
-    <font>
       <b val="1"/>
       <sz val="10"/>
     </font>
@@ -50,7 +45,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -60,11 +55,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="000000A3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EFF3FB"/>
       </patternFill>
     </fill>
   </fills>
@@ -80,17 +70,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -165,6 +152,251 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>econcharts</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>period column (do not edit)</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>pbi / 1000  (miles de millones S/ 2007)</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>cons_priv / 1000</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>inv_bruta_fija_priv / 1000</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>LN(pbi)</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>LN(cons_priv)</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>LN(inv_bruta_fija_priv)</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>100*(pbi/pbi_prev - 1)</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>100*(cons_priv/cons_priv_prev - 1)</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>100*(inv_bruta_fija_priv/inv_prev - 1)</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>100*(ti/ti_prev - 1)  [terms of trade]</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t>100 * cons_priv / pbi</t>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <t>100 * inv_bruta_fija_priv / pbi</t>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0" shapeId="0">
+      <text>
+        <t>100 * (cons_pub + inv_bruta_fija_pub) / pbi</t>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0" shapeId="0">
+      <text>
+        <t>100 * (export - import) / pbi</t>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0" shapeId="0">
+      <text>
+        <t>as-is from BCRP  (% anual)</t>
+      </text>
+    </comment>
+    <comment ref="Q1" authorId="0" shapeId="0">
+      <text>
+        <t>as-is from BCRP  (% PBI; deficit = positive value)</t>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0" shapeId="0">
+      <text>
+        <t>RIN miles de millones USD  [PENDIENTE — BCRP estadisticas anuales]</t>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0" shapeId="0">
+      <text>
+        <t>100*(LN(pbi) - HP_trend)  lambda=100  [PENDIENTE]</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>econcharts</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>period column (do not edit)</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>as-is from BCRP  (soles por USD)</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>100*(tcn / tcn_mes_anterior - 1)  depreciacion mensual %</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>econcharts</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>period column (do not edit)</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>100 * bal_com  / pbi_nominal   (balanza comercial % PBI)</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>100 * bal_ser  / pbi_nominal   (servicios % PBI)</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>100 * ing_prim / pbi_nominal   (renta de factores % PBI)</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>100 * ing_sec  / pbi_nominal   (transferencias % PBI)</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>econcharts</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>period column (do not edit)</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>ingresos del gobierno % PBI  (as-is from BCRP)</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>gasto corriente % PBI  (as-is from BCRP)</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>gasto de capital % PBI  (as-is from BCRP)</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>intereses % PBI  (as-is from BCRP)</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>otros gastos % PBI  (as-is from BCRP)</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>deuda publica % PBI  [PENDIENTE — BCRP estadisticas anuales]</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>econcharts</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>period column (do not edit)</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>LN(PBI per capita USD constante)  WDI: NY.GDP.PCAP.KD  [PENDIENTE]</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>LN(PBI per capita USD constante)  [PENDIENTE]</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>LN(PBI per capita USD constante)  [PENDIENTE]</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>LN(PBI per capita USD constante)  [PENDIENTE]</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -456,28 +688,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S128"/>
+  <dimension ref="A1:S127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -577,716 +809,639 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="42" customHeight="1">
-      <c r="A2" s="2" t="inlineStr"/>
-      <c r="B2" s="2">
-        <f> pbi / 1000</f>
-        <v/>
-      </c>
-      <c r="C2" s="2">
-        <f> cons_priv / 1000</f>
-        <v/>
-      </c>
-      <c r="D2" s="2">
-        <f> inv_bruta_fija_priv / 1000</f>
-        <v/>
-      </c>
-      <c r="E2" s="2">
-        <f> LN(pbi)</f>
-        <v/>
-      </c>
-      <c r="F2" s="2">
-        <f> LN(cons_priv)</f>
-        <v/>
-      </c>
-      <c r="G2" s="2">
-        <f> LN(inv_bruta_fija_priv)</f>
-        <v/>
-      </c>
-      <c r="H2" s="2">
-        <f> 100*(pbi/lag(pbi) - 1)</f>
-        <v/>
-      </c>
-      <c r="I2" s="2">
-        <f> 100*(cons_priv/lag(cons_priv) - 1)</f>
-        <v/>
-      </c>
-      <c r="J2" s="2">
-        <f> 100*(inv_bruta_fija_priv/lag(inv_bruta_fija_priv) - 1)</f>
-        <v/>
-      </c>
-      <c r="K2" s="2">
-        <f> 100*(ti/lag(ti) - 1)  [terms of trade]</f>
-        <v/>
-      </c>
-      <c r="L2" s="2">
-        <f> 100*cons_priv/pbi</f>
-        <v/>
-      </c>
-      <c r="M2" s="2">
-        <f> 100*inv_bruta_fija_priv/pbi</f>
-        <v/>
-      </c>
-      <c r="N2" s="2">
-        <f> 100*(cons_pub+inv_bruta_fija_pub)/pbi</f>
-        <v/>
-      </c>
-      <c r="O2" s="2">
-        <f> 100*(export-import)/pbi</f>
-        <v/>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>as-is from BCRP (annual %)</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>as-is from BCRP (% PBI, deficit = positive)</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>RIN miles de millones USD  [pendiente — BCRP]</t>
-        </is>
-      </c>
-      <c r="S2" s="2">
-        <f> 100*(LN(pbi) - HP_trend)  lambda=100  [pendiente]</f>
-        <v/>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1900</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1900</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1901</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1902</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1903</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1904</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1905</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1906</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1907</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1908</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1909</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1910</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1911</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1912</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1913</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1914</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1915</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1916</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1917</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1918</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1919</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1920</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1921</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1922</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1923</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1924</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1925</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1926</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1927</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1928</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1929</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1930</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1931</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1932</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1933</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1934</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1935</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1936</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1937</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1938</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1939</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1940</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1941</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1942</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1943</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1944</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1945</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1946</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1947</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1948</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1949</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1950</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1951</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1952</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1953</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1954</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1955</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1956</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1957</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1958</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1959</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1960</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1961</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1962</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1963</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1964</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1965</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1966</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>1967</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>1968</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>1969</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>1970</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>1971</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>1972</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1973</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>1974</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>1975</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>1976</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>1977</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1978</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>1979</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>1980</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>1981</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>1982</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>1983</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>1984</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1985</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>1987</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>1988</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>1989</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1990</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>1991</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1992</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1993</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1994</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1995</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1996</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1997</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1998</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1999</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="n">
         <v>2025</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1296,12 +1451,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C390"/>
+  <dimension ref="A1:C389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1321,1960 +1476,1949 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="42" customHeight="1">
-      <c r="A2" s="2" t="inlineStr"/>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>as-is from BCRP (soles/USD)</t>
-        </is>
-      </c>
-      <c r="C2" s="2">
-        <f> 100*(tcn/tcn_prev_month - 1)  depreciacion mensual %</f>
-        <v/>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>34304</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
-        <v>34304</v>
+      <c r="A3" s="2" t="n">
+        <v>34335</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
-        <v>34335</v>
+      <c r="A4" s="2" t="n">
+        <v>34366</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>34366</v>
+      <c r="A5" s="2" t="n">
+        <v>34394</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>34394</v>
+      <c r="A6" s="2" t="n">
+        <v>34425</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>34425</v>
+      <c r="A7" s="2" t="n">
+        <v>34455</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>34455</v>
+      <c r="A8" s="2" t="n">
+        <v>34486</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>34486</v>
+      <c r="A9" s="2" t="n">
+        <v>34516</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>34516</v>
+      <c r="A10" s="2" t="n">
+        <v>34547</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>34547</v>
+      <c r="A11" s="2" t="n">
+        <v>34578</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
-        <v>34578</v>
+      <c r="A12" s="2" t="n">
+        <v>34608</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>34608</v>
+      <c r="A13" s="2" t="n">
+        <v>34639</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
-        <v>34639</v>
+      <c r="A14" s="2" t="n">
+        <v>34669</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>34669</v>
+      <c r="A15" s="2" t="n">
+        <v>34700</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
-        <v>34700</v>
+      <c r="A16" s="2" t="n">
+        <v>34731</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>34731</v>
+      <c r="A17" s="2" t="n">
+        <v>34759</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
-        <v>34759</v>
+      <c r="A18" s="2" t="n">
+        <v>34790</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>34790</v>
+      <c r="A19" s="2" t="n">
+        <v>34820</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
-        <v>34820</v>
+      <c r="A20" s="2" t="n">
+        <v>34851</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
-        <v>34851</v>
+      <c r="A21" s="2" t="n">
+        <v>34881</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
-        <v>34881</v>
+      <c r="A22" s="2" t="n">
+        <v>34912</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
-        <v>34912</v>
+      <c r="A23" s="2" t="n">
+        <v>34943</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
-        <v>34943</v>
+      <c r="A24" s="2" t="n">
+        <v>34973</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
-        <v>34973</v>
+      <c r="A25" s="2" t="n">
+        <v>35004</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
-        <v>35004</v>
+      <c r="A26" s="2" t="n">
+        <v>35034</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
-        <v>35034</v>
+      <c r="A27" s="2" t="n">
+        <v>35065</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
-        <v>35065</v>
+      <c r="A28" s="2" t="n">
+        <v>35096</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
-        <v>35096</v>
+      <c r="A29" s="2" t="n">
+        <v>35125</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
-        <v>35125</v>
+      <c r="A30" s="2" t="n">
+        <v>35156</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
-        <v>35156</v>
+      <c r="A31" s="2" t="n">
+        <v>35186</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
-        <v>35186</v>
+      <c r="A32" s="2" t="n">
+        <v>35217</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
-        <v>35217</v>
+      <c r="A33" s="2" t="n">
+        <v>35247</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
-        <v>35247</v>
+      <c r="A34" s="2" t="n">
+        <v>35278</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
-        <v>35278</v>
+      <c r="A35" s="2" t="n">
+        <v>35309</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
-        <v>35309</v>
+      <c r="A36" s="2" t="n">
+        <v>35339</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
-        <v>35339</v>
+      <c r="A37" s="2" t="n">
+        <v>35370</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
-        <v>35370</v>
+      <c r="A38" s="2" t="n">
+        <v>35400</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
-        <v>35400</v>
+      <c r="A39" s="2" t="n">
+        <v>35431</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
-        <v>35431</v>
+      <c r="A40" s="2" t="n">
+        <v>35462</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
-        <v>35462</v>
+      <c r="A41" s="2" t="n">
+        <v>35490</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
-        <v>35490</v>
+      <c r="A42" s="2" t="n">
+        <v>35521</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
-        <v>35521</v>
+      <c r="A43" s="2" t="n">
+        <v>35551</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
-        <v>35551</v>
+      <c r="A44" s="2" t="n">
+        <v>35582</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
-        <v>35582</v>
+      <c r="A45" s="2" t="n">
+        <v>35612</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
-        <v>35612</v>
+      <c r="A46" s="2" t="n">
+        <v>35643</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
-        <v>35643</v>
+      <c r="A47" s="2" t="n">
+        <v>35674</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
-        <v>35674</v>
+      <c r="A48" s="2" t="n">
+        <v>35704</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
-        <v>35704</v>
+      <c r="A49" s="2" t="n">
+        <v>35735</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
-        <v>35735</v>
+      <c r="A50" s="2" t="n">
+        <v>35765</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
-        <v>35765</v>
+      <c r="A51" s="2" t="n">
+        <v>35796</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
-        <v>35796</v>
+      <c r="A52" s="2" t="n">
+        <v>35827</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
-        <v>35827</v>
+      <c r="A53" s="2" t="n">
+        <v>35855</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
-        <v>35855</v>
+      <c r="A54" s="2" t="n">
+        <v>35886</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
-        <v>35886</v>
+      <c r="A55" s="2" t="n">
+        <v>35916</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
-        <v>35916</v>
+      <c r="A56" s="2" t="n">
+        <v>35947</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
-        <v>35947</v>
+      <c r="A57" s="2" t="n">
+        <v>35977</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
-        <v>35977</v>
+      <c r="A58" s="2" t="n">
+        <v>36008</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
-        <v>36008</v>
+      <c r="A59" s="2" t="n">
+        <v>36039</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
-        <v>36039</v>
+      <c r="A60" s="2" t="n">
+        <v>36069</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
-        <v>36069</v>
+      <c r="A61" s="2" t="n">
+        <v>36100</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
-        <v>36100</v>
+      <c r="A62" s="2" t="n">
+        <v>36130</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
-        <v>36130</v>
+      <c r="A63" s="2" t="n">
+        <v>36161</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
-        <v>36161</v>
+      <c r="A64" s="2" t="n">
+        <v>36192</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
-        <v>36192</v>
+      <c r="A65" s="2" t="n">
+        <v>36220</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
-        <v>36220</v>
+      <c r="A66" s="2" t="n">
+        <v>36251</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
-        <v>36251</v>
+      <c r="A67" s="2" t="n">
+        <v>36281</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
-        <v>36281</v>
+      <c r="A68" s="2" t="n">
+        <v>36312</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="n">
-        <v>36312</v>
+      <c r="A69" s="2" t="n">
+        <v>36342</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="n">
-        <v>36342</v>
+      <c r="A70" s="2" t="n">
+        <v>36373</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="n">
-        <v>36373</v>
+      <c r="A71" s="2" t="n">
+        <v>36404</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="n">
-        <v>36404</v>
+      <c r="A72" s="2" t="n">
+        <v>36434</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="3" t="n">
-        <v>36434</v>
+      <c r="A73" s="2" t="n">
+        <v>36465</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="n">
-        <v>36465</v>
+      <c r="A74" s="2" t="n">
+        <v>36495</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="n">
-        <v>36495</v>
+      <c r="A75" s="2" t="n">
+        <v>36526</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="n">
-        <v>36526</v>
+      <c r="A76" s="2" t="n">
+        <v>36557</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="n">
-        <v>36557</v>
+      <c r="A77" s="2" t="n">
+        <v>36586</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="3" t="n">
-        <v>36586</v>
+      <c r="A78" s="2" t="n">
+        <v>36617</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="n">
-        <v>36617</v>
+      <c r="A79" s="2" t="n">
+        <v>36647</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="3" t="n">
-        <v>36647</v>
+      <c r="A80" s="2" t="n">
+        <v>36678</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="n">
-        <v>36678</v>
+      <c r="A81" s="2" t="n">
+        <v>36708</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="3" t="n">
-        <v>36708</v>
+      <c r="A82" s="2" t="n">
+        <v>36739</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="n">
-        <v>36739</v>
+      <c r="A83" s="2" t="n">
+        <v>36770</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="3" t="n">
-        <v>36770</v>
+      <c r="A84" s="2" t="n">
+        <v>36800</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="n">
-        <v>36800</v>
+      <c r="A85" s="2" t="n">
+        <v>36831</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="3" t="n">
-        <v>36831</v>
+      <c r="A86" s="2" t="n">
+        <v>36861</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="3" t="n">
-        <v>36861</v>
+      <c r="A87" s="2" t="n">
+        <v>36892</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="3" t="n">
-        <v>36892</v>
+      <c r="A88" s="2" t="n">
+        <v>36923</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="3" t="n">
-        <v>36923</v>
+      <c r="A89" s="2" t="n">
+        <v>36951</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="3" t="n">
-        <v>36951</v>
+      <c r="A90" s="2" t="n">
+        <v>36982</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="3" t="n">
-        <v>36982</v>
+      <c r="A91" s="2" t="n">
+        <v>37012</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="3" t="n">
-        <v>37012</v>
+      <c r="A92" s="2" t="n">
+        <v>37043</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="3" t="n">
-        <v>37043</v>
+      <c r="A93" s="2" t="n">
+        <v>37073</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="3" t="n">
-        <v>37073</v>
+      <c r="A94" s="2" t="n">
+        <v>37104</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="3" t="n">
-        <v>37104</v>
+      <c r="A95" s="2" t="n">
+        <v>37135</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="3" t="n">
-        <v>37135</v>
+      <c r="A96" s="2" t="n">
+        <v>37165</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="3" t="n">
-        <v>37165</v>
+      <c r="A97" s="2" t="n">
+        <v>37196</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="3" t="n">
-        <v>37196</v>
+      <c r="A98" s="2" t="n">
+        <v>37226</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="3" t="n">
-        <v>37226</v>
+      <c r="A99" s="2" t="n">
+        <v>37257</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="3" t="n">
-        <v>37257</v>
+      <c r="A100" s="2" t="n">
+        <v>37288</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="3" t="n">
-        <v>37288</v>
+      <c r="A101" s="2" t="n">
+        <v>37316</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="3" t="n">
-        <v>37316</v>
+      <c r="A102" s="2" t="n">
+        <v>37347</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="3" t="n">
-        <v>37347</v>
+      <c r="A103" s="2" t="n">
+        <v>37377</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="3" t="n">
-        <v>37377</v>
+      <c r="A104" s="2" t="n">
+        <v>37408</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="3" t="n">
-        <v>37408</v>
+      <c r="A105" s="2" t="n">
+        <v>37438</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="3" t="n">
-        <v>37438</v>
+      <c r="A106" s="2" t="n">
+        <v>37469</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="3" t="n">
-        <v>37469</v>
+      <c r="A107" s="2" t="n">
+        <v>37500</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="3" t="n">
-        <v>37500</v>
+      <c r="A108" s="2" t="n">
+        <v>37530</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="3" t="n">
-        <v>37530</v>
+      <c r="A109" s="2" t="n">
+        <v>37561</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="3" t="n">
-        <v>37561</v>
+      <c r="A110" s="2" t="n">
+        <v>37591</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="3" t="n">
-        <v>37591</v>
+      <c r="A111" s="2" t="n">
+        <v>37622</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="3" t="n">
-        <v>37622</v>
+      <c r="A112" s="2" t="n">
+        <v>37653</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="3" t="n">
-        <v>37653</v>
+      <c r="A113" s="2" t="n">
+        <v>37681</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="3" t="n">
-        <v>37681</v>
+      <c r="A114" s="2" t="n">
+        <v>37712</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="3" t="n">
-        <v>37712</v>
+      <c r="A115" s="2" t="n">
+        <v>37742</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="3" t="n">
-        <v>37742</v>
+      <c r="A116" s="2" t="n">
+        <v>37773</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="3" t="n">
-        <v>37773</v>
+      <c r="A117" s="2" t="n">
+        <v>37803</v>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="3" t="n">
-        <v>37803</v>
+      <c r="A118" s="2" t="n">
+        <v>37834</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="3" t="n">
-        <v>37834</v>
+      <c r="A119" s="2" t="n">
+        <v>37865</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="3" t="n">
-        <v>37865</v>
+      <c r="A120" s="2" t="n">
+        <v>37895</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="3" t="n">
-        <v>37895</v>
+      <c r="A121" s="2" t="n">
+        <v>37926</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="3" t="n">
-        <v>37926</v>
+      <c r="A122" s="2" t="n">
+        <v>37956</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="3" t="n">
-        <v>37956</v>
+      <c r="A123" s="2" t="n">
+        <v>37987</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="3" t="n">
-        <v>37987</v>
+      <c r="A124" s="2" t="n">
+        <v>38018</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="3" t="n">
-        <v>38018</v>
+      <c r="A125" s="2" t="n">
+        <v>38047</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="3" t="n">
-        <v>38047</v>
+      <c r="A126" s="2" t="n">
+        <v>38078</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="3" t="n">
-        <v>38078</v>
+      <c r="A127" s="2" t="n">
+        <v>38108</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="3" t="n">
-        <v>38108</v>
+      <c r="A128" s="2" t="n">
+        <v>38139</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="3" t="n">
-        <v>38139</v>
+      <c r="A129" s="2" t="n">
+        <v>38169</v>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="3" t="n">
-        <v>38169</v>
+      <c r="A130" s="2" t="n">
+        <v>38200</v>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="3" t="n">
-        <v>38200</v>
+      <c r="A131" s="2" t="n">
+        <v>38231</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="3" t="n">
-        <v>38231</v>
+      <c r="A132" s="2" t="n">
+        <v>38261</v>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="3" t="n">
-        <v>38261</v>
+      <c r="A133" s="2" t="n">
+        <v>38292</v>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="3" t="n">
-        <v>38292</v>
+      <c r="A134" s="2" t="n">
+        <v>38322</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="3" t="n">
-        <v>38322</v>
+      <c r="A135" s="2" t="n">
+        <v>38353</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="3" t="n">
-        <v>38353</v>
+      <c r="A136" s="2" t="n">
+        <v>38384</v>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="3" t="n">
-        <v>38384</v>
+      <c r="A137" s="2" t="n">
+        <v>38412</v>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="3" t="n">
-        <v>38412</v>
+      <c r="A138" s="2" t="n">
+        <v>38443</v>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="3" t="n">
-        <v>38443</v>
+      <c r="A139" s="2" t="n">
+        <v>38473</v>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="3" t="n">
-        <v>38473</v>
+      <c r="A140" s="2" t="n">
+        <v>38504</v>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="3" t="n">
-        <v>38504</v>
+      <c r="A141" s="2" t="n">
+        <v>38534</v>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="3" t="n">
-        <v>38534</v>
+      <c r="A142" s="2" t="n">
+        <v>38565</v>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="3" t="n">
-        <v>38565</v>
+      <c r="A143" s="2" t="n">
+        <v>38596</v>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="3" t="n">
-        <v>38596</v>
+      <c r="A144" s="2" t="n">
+        <v>38626</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="3" t="n">
-        <v>38626</v>
+      <c r="A145" s="2" t="n">
+        <v>38657</v>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="3" t="n">
-        <v>38657</v>
+      <c r="A146" s="2" t="n">
+        <v>38687</v>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="3" t="n">
-        <v>38687</v>
+      <c r="A147" s="2" t="n">
+        <v>38718</v>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="3" t="n">
-        <v>38718</v>
+      <c r="A148" s="2" t="n">
+        <v>38749</v>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="3" t="n">
-        <v>38749</v>
+      <c r="A149" s="2" t="n">
+        <v>38777</v>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="3" t="n">
-        <v>38777</v>
+      <c r="A150" s="2" t="n">
+        <v>38808</v>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="3" t="n">
-        <v>38808</v>
+      <c r="A151" s="2" t="n">
+        <v>38838</v>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="3" t="n">
-        <v>38838</v>
+      <c r="A152" s="2" t="n">
+        <v>38869</v>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="3" t="n">
-        <v>38869</v>
+      <c r="A153" s="2" t="n">
+        <v>38899</v>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="3" t="n">
-        <v>38899</v>
+      <c r="A154" s="2" t="n">
+        <v>38930</v>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="3" t="n">
-        <v>38930</v>
+      <c r="A155" s="2" t="n">
+        <v>38961</v>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="3" t="n">
-        <v>38961</v>
+      <c r="A156" s="2" t="n">
+        <v>38991</v>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="3" t="n">
-        <v>38991</v>
+      <c r="A157" s="2" t="n">
+        <v>39022</v>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="3" t="n">
-        <v>39022</v>
+      <c r="A158" s="2" t="n">
+        <v>39052</v>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="3" t="n">
-        <v>39052</v>
+      <c r="A159" s="2" t="n">
+        <v>39083</v>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="3" t="n">
-        <v>39083</v>
+      <c r="A160" s="2" t="n">
+        <v>39114</v>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="3" t="n">
-        <v>39114</v>
+      <c r="A161" s="2" t="n">
+        <v>39142</v>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="3" t="n">
-        <v>39142</v>
+      <c r="A162" s="2" t="n">
+        <v>39173</v>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="3" t="n">
-        <v>39173</v>
+      <c r="A163" s="2" t="n">
+        <v>39203</v>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="3" t="n">
-        <v>39203</v>
+      <c r="A164" s="2" t="n">
+        <v>39234</v>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="3" t="n">
-        <v>39234</v>
+      <c r="A165" s="2" t="n">
+        <v>39264</v>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="3" t="n">
-        <v>39264</v>
+      <c r="A166" s="2" t="n">
+        <v>39295</v>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="3" t="n">
-        <v>39295</v>
+      <c r="A167" s="2" t="n">
+        <v>39326</v>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="3" t="n">
-        <v>39326</v>
+      <c r="A168" s="2" t="n">
+        <v>39356</v>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="3" t="n">
-        <v>39356</v>
+      <c r="A169" s="2" t="n">
+        <v>39387</v>
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="3" t="n">
-        <v>39387</v>
+      <c r="A170" s="2" t="n">
+        <v>39417</v>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="3" t="n">
-        <v>39417</v>
+      <c r="A171" s="2" t="n">
+        <v>39448</v>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="3" t="n">
-        <v>39448</v>
+      <c r="A172" s="2" t="n">
+        <v>39479</v>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="3" t="n">
-        <v>39479</v>
+      <c r="A173" s="2" t="n">
+        <v>39508</v>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="3" t="n">
-        <v>39508</v>
+      <c r="A174" s="2" t="n">
+        <v>39539</v>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="3" t="n">
-        <v>39539</v>
+      <c r="A175" s="2" t="n">
+        <v>39569</v>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="3" t="n">
-        <v>39569</v>
+      <c r="A176" s="2" t="n">
+        <v>39600</v>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="3" t="n">
-        <v>39600</v>
+      <c r="A177" s="2" t="n">
+        <v>39630</v>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="3" t="n">
-        <v>39630</v>
+      <c r="A178" s="2" t="n">
+        <v>39661</v>
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="3" t="n">
-        <v>39661</v>
+      <c r="A179" s="2" t="n">
+        <v>39692</v>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="3" t="n">
-        <v>39692</v>
+      <c r="A180" s="2" t="n">
+        <v>39722</v>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="3" t="n">
-        <v>39722</v>
+      <c r="A181" s="2" t="n">
+        <v>39753</v>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="3" t="n">
-        <v>39753</v>
+      <c r="A182" s="2" t="n">
+        <v>39783</v>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="3" t="n">
-        <v>39783</v>
+      <c r="A183" s="2" t="n">
+        <v>39814</v>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="3" t="n">
-        <v>39814</v>
+      <c r="A184" s="2" t="n">
+        <v>39845</v>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="3" t="n">
-        <v>39845</v>
+      <c r="A185" s="2" t="n">
+        <v>39873</v>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="3" t="n">
-        <v>39873</v>
+      <c r="A186" s="2" t="n">
+        <v>39904</v>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="3" t="n">
-        <v>39904</v>
+      <c r="A187" s="2" t="n">
+        <v>39934</v>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="3" t="n">
-        <v>39934</v>
+      <c r="A188" s="2" t="n">
+        <v>39965</v>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="3" t="n">
-        <v>39965</v>
+      <c r="A189" s="2" t="n">
+        <v>39995</v>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="3" t="n">
-        <v>39995</v>
+      <c r="A190" s="2" t="n">
+        <v>40026</v>
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="3" t="n">
-        <v>40026</v>
+      <c r="A191" s="2" t="n">
+        <v>40057</v>
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="3" t="n">
-        <v>40057</v>
+      <c r="A192" s="2" t="n">
+        <v>40087</v>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="3" t="n">
-        <v>40087</v>
+      <c r="A193" s="2" t="n">
+        <v>40118</v>
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="3" t="n">
-        <v>40118</v>
+      <c r="A194" s="2" t="n">
+        <v>40148</v>
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="3" t="n">
-        <v>40148</v>
+      <c r="A195" s="2" t="n">
+        <v>40179</v>
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="3" t="n">
-        <v>40179</v>
+      <c r="A196" s="2" t="n">
+        <v>40210</v>
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="3" t="n">
-        <v>40210</v>
+      <c r="A197" s="2" t="n">
+        <v>40238</v>
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="3" t="n">
-        <v>40238</v>
+      <c r="A198" s="2" t="n">
+        <v>40269</v>
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="3" t="n">
-        <v>40269</v>
+      <c r="A199" s="2" t="n">
+        <v>40299</v>
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="3" t="n">
-        <v>40299</v>
+      <c r="A200" s="2" t="n">
+        <v>40330</v>
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="3" t="n">
-        <v>40330</v>
+      <c r="A201" s="2" t="n">
+        <v>40360</v>
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="3" t="n">
-        <v>40360</v>
+      <c r="A202" s="2" t="n">
+        <v>40391</v>
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="3" t="n">
-        <v>40391</v>
+      <c r="A203" s="2" t="n">
+        <v>40422</v>
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="3" t="n">
-        <v>40422</v>
+      <c r="A204" s="2" t="n">
+        <v>40452</v>
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="3" t="n">
-        <v>40452</v>
+      <c r="A205" s="2" t="n">
+        <v>40483</v>
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="3" t="n">
-        <v>40483</v>
+      <c r="A206" s="2" t="n">
+        <v>40513</v>
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="3" t="n">
-        <v>40513</v>
+      <c r="A207" s="2" t="n">
+        <v>40544</v>
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="3" t="n">
-        <v>40544</v>
+      <c r="A208" s="2" t="n">
+        <v>40575</v>
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="3" t="n">
-        <v>40575</v>
+      <c r="A209" s="2" t="n">
+        <v>40603</v>
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="3" t="n">
-        <v>40603</v>
+      <c r="A210" s="2" t="n">
+        <v>40634</v>
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="3" t="n">
-        <v>40634</v>
+      <c r="A211" s="2" t="n">
+        <v>40664</v>
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="3" t="n">
-        <v>40664</v>
+      <c r="A212" s="2" t="n">
+        <v>40695</v>
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="3" t="n">
-        <v>40695</v>
+      <c r="A213" s="2" t="n">
+        <v>40725</v>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="3" t="n">
-        <v>40725</v>
+      <c r="A214" s="2" t="n">
+        <v>40756</v>
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="3" t="n">
-        <v>40756</v>
+      <c r="A215" s="2" t="n">
+        <v>40787</v>
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="3" t="n">
-        <v>40787</v>
+      <c r="A216" s="2" t="n">
+        <v>40817</v>
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="3" t="n">
-        <v>40817</v>
+      <c r="A217" s="2" t="n">
+        <v>40848</v>
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="3" t="n">
-        <v>40848</v>
+      <c r="A218" s="2" t="n">
+        <v>40878</v>
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="3" t="n">
-        <v>40878</v>
+      <c r="A219" s="2" t="n">
+        <v>40909</v>
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="3" t="n">
-        <v>40909</v>
+      <c r="A220" s="2" t="n">
+        <v>40940</v>
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="3" t="n">
-        <v>40940</v>
+      <c r="A221" s="2" t="n">
+        <v>40969</v>
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="3" t="n">
-        <v>40969</v>
+      <c r="A222" s="2" t="n">
+        <v>41000</v>
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="3" t="n">
-        <v>41000</v>
+      <c r="A223" s="2" t="n">
+        <v>41030</v>
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="3" t="n">
-        <v>41030</v>
+      <c r="A224" s="2" t="n">
+        <v>41061</v>
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="3" t="n">
-        <v>41061</v>
+      <c r="A225" s="2" t="n">
+        <v>41091</v>
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="3" t="n">
-        <v>41091</v>
+      <c r="A226" s="2" t="n">
+        <v>41122</v>
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="3" t="n">
-        <v>41122</v>
+      <c r="A227" s="2" t="n">
+        <v>41153</v>
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="3" t="n">
-        <v>41153</v>
+      <c r="A228" s="2" t="n">
+        <v>41183</v>
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="3" t="n">
-        <v>41183</v>
+      <c r="A229" s="2" t="n">
+        <v>41214</v>
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="3" t="n">
-        <v>41214</v>
+      <c r="A230" s="2" t="n">
+        <v>41244</v>
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="3" t="n">
-        <v>41244</v>
+      <c r="A231" s="2" t="n">
+        <v>41275</v>
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="3" t="n">
-        <v>41275</v>
+      <c r="A232" s="2" t="n">
+        <v>41306</v>
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="3" t="n">
-        <v>41306</v>
+      <c r="A233" s="2" t="n">
+        <v>41334</v>
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="3" t="n">
-        <v>41334</v>
+      <c r="A234" s="2" t="n">
+        <v>41365</v>
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="3" t="n">
-        <v>41365</v>
+      <c r="A235" s="2" t="n">
+        <v>41395</v>
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="3" t="n">
-        <v>41395</v>
+      <c r="A236" s="2" t="n">
+        <v>41426</v>
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="3" t="n">
-        <v>41426</v>
+      <c r="A237" s="2" t="n">
+        <v>41456</v>
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="3" t="n">
-        <v>41456</v>
+      <c r="A238" s="2" t="n">
+        <v>41487</v>
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="3" t="n">
-        <v>41487</v>
+      <c r="A239" s="2" t="n">
+        <v>41518</v>
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="3" t="n">
-        <v>41518</v>
+      <c r="A240" s="2" t="n">
+        <v>41548</v>
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="3" t="n">
-        <v>41548</v>
+      <c r="A241" s="2" t="n">
+        <v>41579</v>
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="3" t="n">
-        <v>41579</v>
+      <c r="A242" s="2" t="n">
+        <v>41609</v>
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="3" t="n">
-        <v>41609</v>
+      <c r="A243" s="2" t="n">
+        <v>41640</v>
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="3" t="n">
-        <v>41640</v>
+      <c r="A244" s="2" t="n">
+        <v>41671</v>
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="3" t="n">
-        <v>41671</v>
+      <c r="A245" s="2" t="n">
+        <v>41699</v>
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="3" t="n">
-        <v>41699</v>
+      <c r="A246" s="2" t="n">
+        <v>41730</v>
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="3" t="n">
-        <v>41730</v>
+      <c r="A247" s="2" t="n">
+        <v>41760</v>
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="3" t="n">
-        <v>41760</v>
+      <c r="A248" s="2" t="n">
+        <v>41791</v>
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="3" t="n">
-        <v>41791</v>
+      <c r="A249" s="2" t="n">
+        <v>41821</v>
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="3" t="n">
-        <v>41821</v>
+      <c r="A250" s="2" t="n">
+        <v>41852</v>
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="3" t="n">
-        <v>41852</v>
+      <c r="A251" s="2" t="n">
+        <v>41883</v>
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="3" t="n">
-        <v>41883</v>
+      <c r="A252" s="2" t="n">
+        <v>41913</v>
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="3" t="n">
-        <v>41913</v>
+      <c r="A253" s="2" t="n">
+        <v>41944</v>
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="3" t="n">
-        <v>41944</v>
+      <c r="A254" s="2" t="n">
+        <v>41974</v>
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="3" t="n">
-        <v>41974</v>
+      <c r="A255" s="2" t="n">
+        <v>42005</v>
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="3" t="n">
-        <v>42005</v>
+      <c r="A256" s="2" t="n">
+        <v>42036</v>
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="3" t="n">
-        <v>42036</v>
+      <c r="A257" s="2" t="n">
+        <v>42064</v>
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="3" t="n">
-        <v>42064</v>
+      <c r="A258" s="2" t="n">
+        <v>42095</v>
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="3" t="n">
-        <v>42095</v>
+      <c r="A259" s="2" t="n">
+        <v>42125</v>
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="3" t="n">
-        <v>42125</v>
+      <c r="A260" s="2" t="n">
+        <v>42156</v>
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="3" t="n">
-        <v>42156</v>
+      <c r="A261" s="2" t="n">
+        <v>42186</v>
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="3" t="n">
-        <v>42186</v>
+      <c r="A262" s="2" t="n">
+        <v>42217</v>
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="3" t="n">
-        <v>42217</v>
+      <c r="A263" s="2" t="n">
+        <v>42248</v>
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="3" t="n">
-        <v>42248</v>
+      <c r="A264" s="2" t="n">
+        <v>42278</v>
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="3" t="n">
-        <v>42278</v>
+      <c r="A265" s="2" t="n">
+        <v>42309</v>
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="3" t="n">
-        <v>42309</v>
+      <c r="A266" s="2" t="n">
+        <v>42339</v>
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="3" t="n">
-        <v>42339</v>
+      <c r="A267" s="2" t="n">
+        <v>42370</v>
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="3" t="n">
-        <v>42370</v>
+      <c r="A268" s="2" t="n">
+        <v>42401</v>
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="3" t="n">
-        <v>42401</v>
+      <c r="A269" s="2" t="n">
+        <v>42430</v>
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="3" t="n">
-        <v>42430</v>
+      <c r="A270" s="2" t="n">
+        <v>42461</v>
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="3" t="n">
-        <v>42461</v>
+      <c r="A271" s="2" t="n">
+        <v>42491</v>
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="3" t="n">
-        <v>42491</v>
+      <c r="A272" s="2" t="n">
+        <v>42522</v>
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="3" t="n">
-        <v>42522</v>
+      <c r="A273" s="2" t="n">
+        <v>42552</v>
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="3" t="n">
-        <v>42552</v>
+      <c r="A274" s="2" t="n">
+        <v>42583</v>
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="3" t="n">
-        <v>42583</v>
+      <c r="A275" s="2" t="n">
+        <v>42614</v>
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="3" t="n">
-        <v>42614</v>
+      <c r="A276" s="2" t="n">
+        <v>42644</v>
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="3" t="n">
-        <v>42644</v>
+      <c r="A277" s="2" t="n">
+        <v>42675</v>
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="3" t="n">
-        <v>42675</v>
+      <c r="A278" s="2" t="n">
+        <v>42705</v>
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="3" t="n">
-        <v>42705</v>
+      <c r="A279" s="2" t="n">
+        <v>42736</v>
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="3" t="n">
-        <v>42736</v>
+      <c r="A280" s="2" t="n">
+        <v>42767</v>
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="3" t="n">
-        <v>42767</v>
+      <c r="A281" s="2" t="n">
+        <v>42795</v>
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="3" t="n">
-        <v>42795</v>
+      <c r="A282" s="2" t="n">
+        <v>42826</v>
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="3" t="n">
-        <v>42826</v>
+      <c r="A283" s="2" t="n">
+        <v>42856</v>
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="3" t="n">
-        <v>42856</v>
+      <c r="A284" s="2" t="n">
+        <v>42887</v>
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="3" t="n">
-        <v>42887</v>
+      <c r="A285" s="2" t="n">
+        <v>42917</v>
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="3" t="n">
-        <v>42917</v>
+      <c r="A286" s="2" t="n">
+        <v>42948</v>
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="3" t="n">
-        <v>42948</v>
+      <c r="A287" s="2" t="n">
+        <v>42979</v>
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="3" t="n">
-        <v>42979</v>
+      <c r="A288" s="2" t="n">
+        <v>43009</v>
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="3" t="n">
-        <v>43009</v>
+      <c r="A289" s="2" t="n">
+        <v>43040</v>
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="3" t="n">
-        <v>43040</v>
+      <c r="A290" s="2" t="n">
+        <v>43070</v>
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="3" t="n">
-        <v>43070</v>
+      <c r="A291" s="2" t="n">
+        <v>43101</v>
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="3" t="n">
-        <v>43101</v>
+      <c r="A292" s="2" t="n">
+        <v>43132</v>
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="3" t="n">
-        <v>43132</v>
+      <c r="A293" s="2" t="n">
+        <v>43160</v>
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="3" t="n">
-        <v>43160</v>
+      <c r="A294" s="2" t="n">
+        <v>43191</v>
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="3" t="n">
-        <v>43191</v>
+      <c r="A295" s="2" t="n">
+        <v>43221</v>
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="3" t="n">
-        <v>43221</v>
+      <c r="A296" s="2" t="n">
+        <v>43252</v>
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="3" t="n">
-        <v>43252</v>
+      <c r="A297" s="2" t="n">
+        <v>43282</v>
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="3" t="n">
-        <v>43282</v>
+      <c r="A298" s="2" t="n">
+        <v>43313</v>
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="3" t="n">
-        <v>43313</v>
+      <c r="A299" s="2" t="n">
+        <v>43344</v>
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="3" t="n">
-        <v>43344</v>
+      <c r="A300" s="2" t="n">
+        <v>43374</v>
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="3" t="n">
-        <v>43374</v>
+      <c r="A301" s="2" t="n">
+        <v>43405</v>
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="3" t="n">
-        <v>43405</v>
+      <c r="A302" s="2" t="n">
+        <v>43435</v>
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="3" t="n">
-        <v>43435</v>
+      <c r="A303" s="2" t="n">
+        <v>43466</v>
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="3" t="n">
-        <v>43466</v>
+      <c r="A304" s="2" t="n">
+        <v>43497</v>
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="3" t="n">
-        <v>43497</v>
+      <c r="A305" s="2" t="n">
+        <v>43525</v>
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="3" t="n">
-        <v>43525</v>
+      <c r="A306" s="2" t="n">
+        <v>43556</v>
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="3" t="n">
-        <v>43556</v>
+      <c r="A307" s="2" t="n">
+        <v>43586</v>
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="3" t="n">
-        <v>43586</v>
+      <c r="A308" s="2" t="n">
+        <v>43617</v>
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="3" t="n">
-        <v>43617</v>
+      <c r="A309" s="2" t="n">
+        <v>43647</v>
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="3" t="n">
-        <v>43647</v>
+      <c r="A310" s="2" t="n">
+        <v>43678</v>
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="3" t="n">
-        <v>43678</v>
+      <c r="A311" s="2" t="n">
+        <v>43709</v>
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="3" t="n">
-        <v>43709</v>
+      <c r="A312" s="2" t="n">
+        <v>43739</v>
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="3" t="n">
-        <v>43739</v>
+      <c r="A313" s="2" t="n">
+        <v>43770</v>
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="3" t="n">
-        <v>43770</v>
+      <c r="A314" s="2" t="n">
+        <v>43800</v>
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="3" t="n">
-        <v>43800</v>
+      <c r="A315" s="2" t="n">
+        <v>43831</v>
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="3" t="n">
-        <v>43831</v>
+      <c r="A316" s="2" t="n">
+        <v>43862</v>
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="3" t="n">
-        <v>43862</v>
+      <c r="A317" s="2" t="n">
+        <v>43891</v>
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="3" t="n">
-        <v>43891</v>
+      <c r="A318" s="2" t="n">
+        <v>43922</v>
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="3" t="n">
-        <v>43922</v>
+      <c r="A319" s="2" t="n">
+        <v>43952</v>
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="3" t="n">
-        <v>43952</v>
+      <c r="A320" s="2" t="n">
+        <v>43983</v>
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="3" t="n">
-        <v>43983</v>
+      <c r="A321" s="2" t="n">
+        <v>44013</v>
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="3" t="n">
-        <v>44013</v>
+      <c r="A322" s="2" t="n">
+        <v>44044</v>
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="3" t="n">
-        <v>44044</v>
+      <c r="A323" s="2" t="n">
+        <v>44075</v>
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="3" t="n">
-        <v>44075</v>
+      <c r="A324" s="2" t="n">
+        <v>44105</v>
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="3" t="n">
-        <v>44105</v>
+      <c r="A325" s="2" t="n">
+        <v>44136</v>
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="3" t="n">
-        <v>44136</v>
+      <c r="A326" s="2" t="n">
+        <v>44166</v>
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="3" t="n">
-        <v>44166</v>
+      <c r="A327" s="2" t="n">
+        <v>44197</v>
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="3" t="n">
-        <v>44197</v>
+      <c r="A328" s="2" t="n">
+        <v>44228</v>
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="3" t="n">
-        <v>44228</v>
+      <c r="A329" s="2" t="n">
+        <v>44256</v>
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="3" t="n">
-        <v>44256</v>
+      <c r="A330" s="2" t="n">
+        <v>44287</v>
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="3" t="n">
-        <v>44287</v>
+      <c r="A331" s="2" t="n">
+        <v>44317</v>
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="3" t="n">
-        <v>44317</v>
+      <c r="A332" s="2" t="n">
+        <v>44348</v>
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="3" t="n">
-        <v>44348</v>
+      <c r="A333" s="2" t="n">
+        <v>44378</v>
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="3" t="n">
-        <v>44378</v>
+      <c r="A334" s="2" t="n">
+        <v>44409</v>
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="3" t="n">
-        <v>44409</v>
+      <c r="A335" s="2" t="n">
+        <v>44440</v>
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="3" t="n">
-        <v>44440</v>
+      <c r="A336" s="2" t="n">
+        <v>44470</v>
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="3" t="n">
-        <v>44470</v>
+      <c r="A337" s="2" t="n">
+        <v>44501</v>
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="3" t="n">
-        <v>44501</v>
+      <c r="A338" s="2" t="n">
+        <v>44531</v>
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="3" t="n">
-        <v>44531</v>
+      <c r="A339" s="2" t="n">
+        <v>44562</v>
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="3" t="n">
-        <v>44562</v>
+      <c r="A340" s="2" t="n">
+        <v>44593</v>
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="3" t="n">
-        <v>44593</v>
+      <c r="A341" s="2" t="n">
+        <v>44621</v>
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="3" t="n">
-        <v>44621</v>
+      <c r="A342" s="2" t="n">
+        <v>44652</v>
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="3" t="n">
-        <v>44652</v>
+      <c r="A343" s="2" t="n">
+        <v>44682</v>
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="3" t="n">
-        <v>44682</v>
+      <c r="A344" s="2" t="n">
+        <v>44713</v>
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="3" t="n">
-        <v>44713</v>
+      <c r="A345" s="2" t="n">
+        <v>44743</v>
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="3" t="n">
-        <v>44743</v>
+      <c r="A346" s="2" t="n">
+        <v>44774</v>
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="3" t="n">
-        <v>44774</v>
+      <c r="A347" s="2" t="n">
+        <v>44805</v>
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="3" t="n">
-        <v>44805</v>
+      <c r="A348" s="2" t="n">
+        <v>44835</v>
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="3" t="n">
-        <v>44835</v>
+      <c r="A349" s="2" t="n">
+        <v>44866</v>
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="3" t="n">
-        <v>44866</v>
+      <c r="A350" s="2" t="n">
+        <v>44896</v>
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="3" t="n">
-        <v>44896</v>
+      <c r="A351" s="2" t="n">
+        <v>44927</v>
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="3" t="n">
-        <v>44927</v>
+      <c r="A352" s="2" t="n">
+        <v>44958</v>
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="3" t="n">
-        <v>44958</v>
+      <c r="A353" s="2" t="n">
+        <v>44986</v>
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="3" t="n">
-        <v>44986</v>
+      <c r="A354" s="2" t="n">
+        <v>45017</v>
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="3" t="n">
-        <v>45017</v>
+      <c r="A355" s="2" t="n">
+        <v>45047</v>
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="3" t="n">
-        <v>45047</v>
+      <c r="A356" s="2" t="n">
+        <v>45078</v>
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="3" t="n">
-        <v>45078</v>
+      <c r="A357" s="2" t="n">
+        <v>45108</v>
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="3" t="n">
-        <v>45108</v>
+      <c r="A358" s="2" t="n">
+        <v>45139</v>
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="3" t="n">
-        <v>45139</v>
+      <c r="A359" s="2" t="n">
+        <v>45170</v>
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="3" t="n">
-        <v>45170</v>
+      <c r="A360" s="2" t="n">
+        <v>45200</v>
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="3" t="n">
-        <v>45200</v>
+      <c r="A361" s="2" t="n">
+        <v>45231</v>
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="3" t="n">
-        <v>45231</v>
+      <c r="A362" s="2" t="n">
+        <v>45261</v>
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="3" t="n">
-        <v>45261</v>
+      <c r="A363" s="2" t="n">
+        <v>45292</v>
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="3" t="n">
-        <v>45292</v>
+      <c r="A364" s="2" t="n">
+        <v>45323</v>
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="3" t="n">
-        <v>45323</v>
+      <c r="A365" s="2" t="n">
+        <v>45352</v>
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="3" t="n">
-        <v>45352</v>
+      <c r="A366" s="2" t="n">
+        <v>45383</v>
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="3" t="n">
-        <v>45383</v>
+      <c r="A367" s="2" t="n">
+        <v>45413</v>
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="3" t="n">
-        <v>45413</v>
+      <c r="A368" s="2" t="n">
+        <v>45444</v>
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="3" t="n">
-        <v>45444</v>
+      <c r="A369" s="2" t="n">
+        <v>45474</v>
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="3" t="n">
-        <v>45474</v>
+      <c r="A370" s="2" t="n">
+        <v>45505</v>
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="3" t="n">
-        <v>45505</v>
+      <c r="A371" s="2" t="n">
+        <v>45536</v>
       </c>
     </row>
     <row r="372">
-      <c r="A372" s="3" t="n">
-        <v>45536</v>
+      <c r="A372" s="2" t="n">
+        <v>45566</v>
       </c>
     </row>
     <row r="373">
-      <c r="A373" s="3" t="n">
-        <v>45566</v>
+      <c r="A373" s="2" t="n">
+        <v>45597</v>
       </c>
     </row>
     <row r="374">
-      <c r="A374" s="3" t="n">
-        <v>45597</v>
+      <c r="A374" s="2" t="n">
+        <v>45627</v>
       </c>
     </row>
     <row r="375">
-      <c r="A375" s="3" t="n">
-        <v>45627</v>
+      <c r="A375" s="2" t="n">
+        <v>45658</v>
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="3" t="n">
-        <v>45658</v>
+      <c r="A376" s="2" t="n">
+        <v>45689</v>
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="3" t="n">
-        <v>45689</v>
+      <c r="A377" s="2" t="n">
+        <v>45717</v>
       </c>
     </row>
     <row r="378">
-      <c r="A378" s="3" t="n">
-        <v>45717</v>
+      <c r="A378" s="2" t="n">
+        <v>45748</v>
       </c>
     </row>
     <row r="379">
-      <c r="A379" s="3" t="n">
-        <v>45748</v>
+      <c r="A379" s="2" t="n">
+        <v>45778</v>
       </c>
     </row>
     <row r="380">
-      <c r="A380" s="3" t="n">
-        <v>45778</v>
+      <c r="A380" s="2" t="n">
+        <v>45809</v>
       </c>
     </row>
     <row r="381">
-      <c r="A381" s="3" t="n">
-        <v>45809</v>
+      <c r="A381" s="2" t="n">
+        <v>45839</v>
       </c>
     </row>
     <row r="382">
-      <c r="A382" s="3" t="n">
-        <v>45839</v>
+      <c r="A382" s="2" t="n">
+        <v>45870</v>
       </c>
     </row>
     <row r="383">
-      <c r="A383" s="3" t="n">
-        <v>45870</v>
+      <c r="A383" s="2" t="n">
+        <v>45901</v>
       </c>
     </row>
     <row r="384">
-      <c r="A384" s="3" t="n">
-        <v>45901</v>
+      <c r="A384" s="2" t="n">
+        <v>45931</v>
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="3" t="n">
-        <v>45931</v>
+      <c r="A385" s="2" t="n">
+        <v>45962</v>
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="3" t="n">
-        <v>45962</v>
+      <c r="A386" s="2" t="n">
+        <v>45992</v>
       </c>
     </row>
     <row r="387">
-      <c r="A387" s="3" t="n">
-        <v>45992</v>
+      <c r="A387" s="2" t="n">
+        <v>46023</v>
       </c>
     </row>
     <row r="388">
-      <c r="A388" s="3" t="n">
-        <v>46023</v>
+      <c r="A388" s="2" t="n">
+        <v>46054</v>
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="3" t="n">
-        <v>46054</v>
-      </c>
-    </row>
-    <row r="390">
-      <c r="A390" s="3" t="n">
+      <c r="A389" s="2" t="n">
         <v>46082</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -3284,14 +3428,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E78"/>
+  <dimension ref="A1:E77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3321,407 +3465,389 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="42" customHeight="1">
-      <c r="A2" s="2" t="inlineStr"/>
-      <c r="B2" s="2">
-        <f> 100*bal_com/pbi_nominal   balanza comercial</f>
-        <v/>
-      </c>
-      <c r="C2" s="2">
-        <f> 100*bal_ser/pbi_nominal   servicios</f>
-        <v/>
-      </c>
-      <c r="D2" s="2">
-        <f> 100*ing_prim/pbi_nominal  renta de factores</f>
-        <v/>
-      </c>
-      <c r="E2" s="2">
-        <f> 100*ing_sec/pbi_nominal   transferencias</f>
-        <v/>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1950</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1950</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1951</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1952</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1953</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1954</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1955</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1956</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1957</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1958</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1959</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1960</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1961</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1962</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1963</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1964</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1965</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1966</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1967</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1968</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1969</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1970</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1971</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1972</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1973</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1974</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1975</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1976</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1977</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1978</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1979</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1980</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1981</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1982</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1983</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1984</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1985</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1987</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1988</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1989</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1990</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1991</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1992</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1993</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1994</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1995</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1996</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1997</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1998</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1999</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
         <v>2025</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -3731,16 +3857,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3780,321 +3906,289 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="42" customHeight="1">
-      <c r="A2" s="2" t="inlineStr"/>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>ingresos % PBI  as-is from BCRP</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>gasto corriente % PBI  as-is from BCRP</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>gasto de capital % PBI  as-is from BCRP</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>intereses % PBI  as-is from BCRP</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>otros gastos % PBI  as-is from BCRP</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>deuda publica % PBI  [pendiente — BCRP]</t>
-        </is>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1970</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1970</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1971</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1972</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1973</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1974</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1975</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1976</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1977</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1978</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1979</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1980</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1981</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1982</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1983</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1984</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1985</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1987</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1988</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1989</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1990</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1991</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1992</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1993</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1994</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1995</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1996</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1997</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1998</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1999</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
         <v>2025</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -4104,14 +4198,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4141,356 +4235,334 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="42" customHeight="1">
-      <c r="A2" s="2" t="inlineStr"/>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>LN(PBI pc USD const)  WDI: NY.GDP.PCAP.KD  [pendiente]</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>LN(PBI pc USD const)  [pendiente]</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>LN(PBI pc USD const)  [pendiente]</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>LN(PBI pc USD const)  [pendiente]</t>
-        </is>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1960</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1960</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1961</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1962</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1963</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1964</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1965</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1966</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1967</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1968</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1969</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1970</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1971</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1972</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1973</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1974</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1975</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1976</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1977</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1978</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1979</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1980</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1981</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1982</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1983</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1984</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1985</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1987</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1988</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1989</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1990</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1991</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1992</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1993</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1994</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1995</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1996</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1997</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1998</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1999</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
         <v>2024</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -4501,161 +4573,182 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>MACRO.XLSX — skeleton for examples/macro/peru_macro.yaml</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr"/>
+      <c r="A2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>FLUJO DE TRABAJO</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1. Pega los datos del addin BCRP en cada hoja (columna de periodo ya esta).</t>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1. Pega los datos del addin BCRP en cada hoja (la columna de periodo ya esta pre-llenada).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. Las columnas marcadas 'as-is' se usan directamente sin transformacion.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  3. Las columnas con formula deben calcularse en Excel antes de usar el batch.</t>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3. Las columnas con formula se calculan en Excel antes de correr el batch.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Pasa el cursor sobre cada encabezado de columna para ver la formula.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  4. Corre:  econcharts build peru_macro.yaml</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr"/>
-    </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>HOJAS Y RANGOS DE PERIODO</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  anual   — anual 1900-2025   (columna 'year', entero)</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  mensual — mensual dic-1993 a mar-2026  (columna 'month', fecha)</t>
-        </is>
-      </c>
-    </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  bdp     — anual 1950-2025   (balanza de pagos)</t>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  mensual — mensual dic-1993 a mar-2026  (columna 'month', fecha YYYY-MM-DD)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  bdp     — anual 1950-2025   (balanza de pagos corriente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  fiscal  — anual 1970-2025   (datos fiscales)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  pbi_pc  — anual 1960-2024   [pendiente datos externos, chart A]</t>
-        </is>
-      </c>
-    </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr"/>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  pbi_pc  — anual 1960-2024   [pendiente datos externos — chart A]</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>COLUMNAS PENDIENTES (datos no disponibles en el Excel actual)</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  rin       (anual)  — BCRP estadisticas anuales reservas internacionales</t>
-        </is>
-      </c>
-    </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  deuda_pub (fiscal) — BCRP estadisticas anuales sector publico</t>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  rin       (anual)   — BCRP estadisticas anuales / reservas internacionales</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  pbi_pc/*  (pbi_pc) — WDI NY.GDP.PCAP.KD o Maddison Project</t>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  deuda_pub (fiscal)  — BCRP estadisticas anuales / sector publico</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  brecha_pbi(anual)  — requiere filtro HP (lambda=100) sobre ln(pbi)</t>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  pbi_pc/* (pbi_pc)   — WDI indicador NY.GDP.PCAP.KD  o  Maddison Project</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr"/>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  brecha_pbi (anual)  — requiere filtro HP (lambda=100) sobre LN(pbi)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>DIFERENCIAS VS EL SCRIPT R</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  TCN:       el grafico de 2 paneles (facet) se divide en tcn_nivel + tcn_dep.</t>
-        </is>
-      </c>
-    </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Inflacion: el grafico con eje-y recortado se reemplaza por infla_reciente (1993:2025).</t>
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Graph 10 (TCN): el grafico de 2 paneles (facet_wrap) se divide en</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    tcn_nivel + tcn_dep — econcharts no tiene facets aun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Graph 6 (inflacion recortada): reemplazado por infla_reciente (period 1993:2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    porque econcharts no tiene opcion de ylim en el spec.</t>
         </is>
       </c>
     </row>
